--- a/exports/sol-usd_predictions_last90.xlsx
+++ b/exports/sol-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>189.77</v>
+        <v>183.07</v>
       </c>
       <c r="C2" t="n">
-        <v>187.74</v>
+        <v>187.82</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.03</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>191.16</v>
+        <v>176.11</v>
       </c>
       <c r="C3" t="n">
-        <v>190.72</v>
+        <v>180.33</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.44</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>183.07</v>
+        <v>187.59</v>
       </c>
       <c r="C4" t="n">
-        <v>187.83</v>
+        <v>179.39</v>
       </c>
       <c r="D4" t="n">
-        <v>4.76</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>176.11</v>
+        <v>180.28</v>
       </c>
       <c r="C5" t="n">
-        <v>180.34</v>
+        <v>185.26</v>
       </c>
       <c r="D5" t="n">
-        <v>4.23</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>187.59</v>
+        <v>200.65</v>
       </c>
       <c r="C6" t="n">
-        <v>179.4</v>
+        <v>184.46</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.19</v>
+        <v>-16.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180.28</v>
+        <v>203.94</v>
       </c>
       <c r="C7" t="n">
-        <v>185.26</v>
+        <v>200.07</v>
       </c>
       <c r="D7" t="n">
-        <v>4.98</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>200.65</v>
+        <v>205.85</v>
       </c>
       <c r="C8" t="n">
-        <v>184.47</v>
+        <v>204.24</v>
       </c>
       <c r="D8" t="n">
-        <v>-16.17</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203.94</v>
+        <v>187.28</v>
       </c>
       <c r="C9" t="n">
-        <v>200.07</v>
+        <v>201.12</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.87</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>205.85</v>
+        <v>195.91</v>
       </c>
       <c r="C10" t="n">
-        <v>204.25</v>
+        <v>190.21</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.61</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>187.28</v>
+        <v>202.92</v>
       </c>
       <c r="C11" t="n">
-        <v>201.13</v>
+        <v>197.4</v>
       </c>
       <c r="D11" t="n">
-        <v>13.85</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>195.91</v>
+        <v>214.41</v>
       </c>
       <c r="C12" t="n">
-        <v>190.23</v>
+        <v>204.22</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.68</v>
+        <v>-10.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>202.92</v>
+        <v>205.22</v>
       </c>
       <c r="C13" t="n">
-        <v>197.4</v>
+        <v>210.63</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.52</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>214.41</v>
+        <v>202.86</v>
       </c>
       <c r="C14" t="n">
-        <v>204.22</v>
+        <v>205.42</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.19</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>205.22</v>
+        <v>200.86</v>
       </c>
       <c r="C15" t="n">
-        <v>210.63</v>
+        <v>203.95</v>
       </c>
       <c r="D15" t="n">
-        <v>5.41</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>202.86</v>
+        <v>197.11</v>
       </c>
       <c r="C16" t="n">
-        <v>205.43</v>
+        <v>200.15</v>
       </c>
       <c r="D16" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>200.86</v>
+        <v>209.48</v>
       </c>
       <c r="C17" t="n">
-        <v>203.95</v>
+        <v>199.33</v>
       </c>
       <c r="D17" t="n">
-        <v>3.09</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>197.11</v>
+        <v>210.75</v>
       </c>
       <c r="C18" t="n">
-        <v>200.16</v>
+        <v>208.67</v>
       </c>
       <c r="D18" t="n">
-        <v>3.05</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>209.48</v>
+        <v>202.56</v>
       </c>
       <c r="C19" t="n">
-        <v>199.33</v>
+        <v>209.22</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.15</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>210.75</v>
+        <v>203.5</v>
       </c>
       <c r="C20" t="n">
-        <v>208.67</v>
+        <v>202.63</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.08</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>202.56</v>
+        <v>200.25</v>
       </c>
       <c r="C21" t="n">
-        <v>209.23</v>
+        <v>203.31</v>
       </c>
       <c r="D21" t="n">
-        <v>6.67</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>203.5</v>
+        <v>206.47</v>
       </c>
       <c r="C22" t="n">
-        <v>202.64</v>
+        <v>201.67</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.86</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>200.25</v>
+        <v>214.19</v>
       </c>
       <c r="C23" t="n">
-        <v>203.31</v>
+        <v>206.24</v>
       </c>
       <c r="D23" t="n">
-        <v>3.07</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>206.47</v>
+        <v>217.25</v>
       </c>
       <c r="C24" t="n">
-        <v>201.67</v>
+        <v>213.97</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>214.19</v>
+        <v>223.99</v>
       </c>
       <c r="C25" t="n">
-        <v>206.25</v>
+        <v>218.31</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.94</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>217.25</v>
+        <v>228.76</v>
       </c>
       <c r="C26" t="n">
-        <v>213.97</v>
+        <v>223.7</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.28</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>223.99</v>
+        <v>242.3</v>
       </c>
       <c r="C27" t="n">
-        <v>218.31</v>
+        <v>230.02</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.68</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>228.76</v>
+        <v>242.6</v>
       </c>
       <c r="C28" t="n">
-        <v>223.7</v>
+        <v>240.63</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.05</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>242.3</v>
+        <v>240.56</v>
       </c>
       <c r="C29" t="n">
-        <v>230.02</v>
+        <v>240.99</v>
       </c>
       <c r="D29" t="n">
-        <v>-12.28</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>242.6</v>
+        <v>234.36</v>
       </c>
       <c r="C30" t="n">
-        <v>240.63</v>
+        <v>238.54</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.96</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>240.56</v>
+        <v>236.99</v>
       </c>
       <c r="C31" t="n">
-        <v>240.99</v>
+        <v>234.75</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>234.36</v>
+        <v>244.86</v>
       </c>
       <c r="C32" t="n">
-        <v>238.54</v>
+        <v>237.81</v>
       </c>
       <c r="D32" t="n">
-        <v>4.18</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>236.99</v>
+        <v>247.64</v>
       </c>
       <c r="C33" t="n">
-        <v>234.76</v>
+        <v>244.46</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.23</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>244.86</v>
+        <v>238.55</v>
       </c>
       <c r="C34" t="n">
-        <v>237.82</v>
+        <v>245.16</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.04</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>247.64</v>
+        <v>239.59</v>
       </c>
       <c r="C35" t="n">
-        <v>244.46</v>
+        <v>239.43</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.17</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>238.55</v>
+        <v>236.58</v>
       </c>
       <c r="C36" t="n">
-        <v>245.16</v>
+        <v>238.99</v>
       </c>
       <c r="D36" t="n">
-        <v>6.61</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>239.59</v>
+        <v>220.5</v>
       </c>
       <c r="C37" t="n">
-        <v>239.44</v>
+        <v>232.07</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.16</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>236.58</v>
+        <v>213.72</v>
       </c>
       <c r="C38" t="n">
-        <v>238.99</v>
+        <v>218.74</v>
       </c>
       <c r="D38" t="n">
-        <v>2.41</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>220.5</v>
+        <v>211.76</v>
       </c>
       <c r="C39" t="n">
-        <v>232.08</v>
+        <v>213.78</v>
       </c>
       <c r="D39" t="n">
-        <v>11.59</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>213.72</v>
+        <v>192.38</v>
       </c>
       <c r="C40" t="n">
-        <v>218.76</v>
+        <v>207.21</v>
       </c>
       <c r="D40" t="n">
-        <v>5.04</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>211.76</v>
+        <v>205.35</v>
       </c>
       <c r="C41" t="n">
-        <v>213.8</v>
+        <v>195.87</v>
       </c>
       <c r="D41" t="n">
-        <v>2.04</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>192.38</v>
+        <v>203.58</v>
       </c>
       <c r="C42" t="n">
-        <v>207.22</v>
+        <v>204.83</v>
       </c>
       <c r="D42" t="n">
-        <v>14.84</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>205.35</v>
+        <v>210.74</v>
       </c>
       <c r="C43" t="n">
-        <v>195.88</v>
+        <v>206.27</v>
       </c>
       <c r="D43" t="n">
-        <v>-9.470000000000001</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>203.58</v>
+        <v>213.05</v>
       </c>
       <c r="C44" t="n">
-        <v>204.83</v>
+        <v>210.56</v>
       </c>
       <c r="D44" t="n">
-        <v>1.25</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>210.74</v>
+        <v>208.74</v>
       </c>
       <c r="C45" t="n">
-        <v>206.28</v>
+        <v>212.8</v>
       </c>
       <c r="D45" t="n">
-        <v>-4.46</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>213.05</v>
+        <v>221.68</v>
       </c>
       <c r="C46" t="n">
-        <v>210.56</v>
+        <v>212.41</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.49</v>
+        <v>-9.26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>208.74</v>
+        <v>234.86</v>
       </c>
       <c r="C47" t="n">
-        <v>212.81</v>
+        <v>222.68</v>
       </c>
       <c r="D47" t="n">
-        <v>4.06</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>221.68</v>
+        <v>233</v>
       </c>
       <c r="C48" t="n">
-        <v>212.42</v>
+        <v>233.09</v>
       </c>
       <c r="D48" t="n">
-        <v>-9.26</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>234.86</v>
+        <v>228</v>
       </c>
       <c r="C49" t="n">
-        <v>222.68</v>
+        <v>231.12</v>
       </c>
       <c r="D49" t="n">
-        <v>-12.18</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>233</v>
+        <v>228.6</v>
       </c>
       <c r="C50" t="n">
-        <v>233.09</v>
+        <v>227.85</v>
       </c>
       <c r="D50" t="n">
-        <v>0.09</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>228</v>
+        <v>232.52</v>
       </c>
       <c r="C51" t="n">
-        <v>231.13</v>
+        <v>229.65</v>
       </c>
       <c r="D51" t="n">
-        <v>3.13</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>228.6</v>
+        <v>220.48</v>
       </c>
       <c r="C52" t="n">
-        <v>227.86</v>
+        <v>228.84</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.74</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>232.52</v>
+        <v>229.1</v>
       </c>
       <c r="C53" t="n">
-        <v>229.66</v>
+        <v>221.57</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.86</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>220.48</v>
+        <v>220.99</v>
       </c>
       <c r="C54" t="n">
-        <v>228.85</v>
+        <v>226.76</v>
       </c>
       <c r="D54" t="n">
-        <v>8.369999999999999</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>229.1</v>
+        <v>188.66</v>
       </c>
       <c r="C55" t="n">
-        <v>221.58</v>
+        <v>212.97</v>
       </c>
       <c r="D55" t="n">
-        <v>-7.52</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>220.99</v>
+        <v>178.05</v>
       </c>
       <c r="C56" t="n">
-        <v>226.76</v>
+        <v>185.28</v>
       </c>
       <c r="D56" t="n">
-        <v>5.77</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>188.66</v>
+        <v>197.51</v>
       </c>
       <c r="C57" t="n">
-        <v>212.99</v>
+        <v>183.19</v>
       </c>
       <c r="D57" t="n">
-        <v>24.32</v>
+        <v>-14.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>178.05</v>
+        <v>208.37</v>
       </c>
       <c r="C58" t="n">
-        <v>185.31</v>
+        <v>199.45</v>
       </c>
       <c r="D58" t="n">
-        <v>7.26</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>197.51</v>
+        <v>202.46</v>
       </c>
       <c r="C59" t="n">
-        <v>183.2</v>
+        <v>204.71</v>
       </c>
       <c r="D59" t="n">
-        <v>-14.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>208.37</v>
+        <v>194.02</v>
       </c>
       <c r="C60" t="n">
-        <v>199.45</v>
+        <v>200.51</v>
       </c>
       <c r="D60" t="n">
-        <v>-8.92</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>202.46</v>
+        <v>184.69</v>
       </c>
       <c r="C61" t="n">
-        <v>204.72</v>
+        <v>194.17</v>
       </c>
       <c r="D61" t="n">
-        <v>2.25</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>194.02</v>
+        <v>182.03</v>
       </c>
       <c r="C62" t="n">
-        <v>200.52</v>
+        <v>184.61</v>
       </c>
       <c r="D62" t="n">
-        <v>6.5</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>184.69</v>
+        <v>187.66</v>
       </c>
       <c r="C63" t="n">
-        <v>194.19</v>
+        <v>181.95</v>
       </c>
       <c r="D63" t="n">
-        <v>9.5</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>182.03</v>
+        <v>187.8</v>
       </c>
       <c r="C64" t="n">
-        <v>184.64</v>
+        <v>185.67</v>
       </c>
       <c r="D64" t="n">
-        <v>2.6</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>187.66</v>
+        <v>189.75</v>
       </c>
       <c r="C65" t="n">
-        <v>181.97</v>
+        <v>186.9</v>
       </c>
       <c r="D65" t="n">
-        <v>-5.69</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B66" t="n">
+        <v>185.67</v>
+      </c>
+      <c r="C66" t="n">
         <v>187.8</v>
       </c>
-      <c r="C66" t="n">
-        <v>185.68</v>
-      </c>
       <c r="D66" t="n">
-        <v>-2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>189.75</v>
+        <v>180.15</v>
       </c>
       <c r="C67" t="n">
-        <v>186.91</v>
+        <v>184.41</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.84</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>185.67</v>
+        <v>191.39</v>
       </c>
       <c r="C68" t="n">
-        <v>187.81</v>
+        <v>182.68</v>
       </c>
       <c r="D68" t="n">
-        <v>2.14</v>
+        <v>-8.710000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>180.15</v>
+        <v>193.56</v>
       </c>
       <c r="C69" t="n">
-        <v>184.43</v>
+        <v>190.59</v>
       </c>
       <c r="D69" t="n">
-        <v>4.28</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>191.39</v>
+        <v>194.04</v>
       </c>
       <c r="C70" t="n">
-        <v>182.69</v>
+        <v>193.12</v>
       </c>
       <c r="D70" t="n">
-        <v>-8.69</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>193.56</v>
+        <v>200.03</v>
       </c>
       <c r="C71" t="n">
-        <v>190.6</v>
+        <v>193.93</v>
       </c>
       <c r="D71" t="n">
-        <v>-2.96</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>194.04</v>
+        <v>198.74</v>
       </c>
       <c r="C72" t="n">
-        <v>193.13</v>
+        <v>199.29</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.91</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>200.03</v>
+        <v>194.44</v>
       </c>
       <c r="C73" t="n">
-        <v>193.94</v>
+        <v>197.11</v>
       </c>
       <c r="D73" t="n">
-        <v>-6.09</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>198.74</v>
+        <v>194.41</v>
       </c>
       <c r="C74" t="n">
-        <v>199.3</v>
+        <v>193.19</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>194.44</v>
+        <v>184.62</v>
       </c>
       <c r="C75" t="n">
-        <v>197.12</v>
+        <v>191.28</v>
       </c>
       <c r="D75" t="n">
-        <v>2.68</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>194.41</v>
+        <v>187.21</v>
       </c>
       <c r="C76" t="n">
-        <v>193.2</v>
+        <v>184.56</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.21</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>184.62</v>
+        <v>186.38</v>
       </c>
       <c r="C77" t="n">
-        <v>191.29</v>
+        <v>185.51</v>
       </c>
       <c r="D77" t="n">
-        <v>6.67</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>187.21</v>
+        <v>187.83</v>
       </c>
       <c r="C78" t="n">
-        <v>184.58</v>
+        <v>185.62</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.63</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>186.38</v>
+        <v>166.09</v>
       </c>
       <c r="C79" t="n">
-        <v>185.52</v>
+        <v>180.03</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.86</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>187.83</v>
+        <v>155.4</v>
       </c>
       <c r="C80" t="n">
-        <v>185.64</v>
+        <v>162.26</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.19</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>166.09</v>
+        <v>162.57</v>
       </c>
       <c r="C81" t="n">
-        <v>180.05</v>
+        <v>157.48</v>
       </c>
       <c r="D81" t="n">
-        <v>13.96</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>155.4</v>
+        <v>155.07</v>
       </c>
       <c r="C82" t="n">
-        <v>162.29</v>
+        <v>159.55</v>
       </c>
       <c r="D82" t="n">
-        <v>6.89</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>162.57</v>
+        <v>161.71</v>
       </c>
       <c r="C83" t="n">
-        <v>157.5</v>
+        <v>155.36</v>
       </c>
       <c r="D83" t="n">
-        <v>-5.07</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>155.07</v>
+        <v>158.1</v>
       </c>
       <c r="C84" t="n">
-        <v>159.57</v>
+        <v>159.59</v>
       </c>
       <c r="D84" t="n">
-        <v>4.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>161.71</v>
+        <v>164.45</v>
       </c>
       <c r="C85" t="n">
-        <v>155.38</v>
+        <v>161.78</v>
       </c>
       <c r="D85" t="n">
-        <v>-6.33</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>158.1</v>
+        <v>167.37</v>
       </c>
       <c r="C86" t="n">
-        <v>159.6</v>
+        <v>165.35</v>
       </c>
       <c r="D86" t="n">
-        <v>1.5</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>164.45</v>
+        <v>154.57</v>
       </c>
       <c r="C87" t="n">
-        <v>161.79</v>
+        <v>163.08</v>
       </c>
       <c r="D87" t="n">
-        <v>-2.66</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>167.37</v>
+        <v>153.26</v>
       </c>
       <c r="C88" t="n">
-        <v>165.36</v>
+        <v>154.01</v>
       </c>
       <c r="D88" t="n">
-        <v>-2.01</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>154.57</v>
+        <v>145.11</v>
       </c>
       <c r="C89" t="n">
-        <v>163.09</v>
+        <v>150.33</v>
       </c>
       <c r="D89" t="n">
-        <v>8.52</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>153.26</v>
+        <v>138.68</v>
       </c>
       <c r="C90" t="n">
-        <v>154.03</v>
+        <v>142.96</v>
       </c>
       <c r="D90" t="n">
-        <v>0.76</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>145.11</v>
+        <v>139.54</v>
       </c>
       <c r="C91" t="n">
-        <v>150.35</v>
+        <v>138.27</v>
       </c>
       <c r="D91" t="n">
-        <v>5.24</v>
+        <v>-1.27</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sol-usd_predictions_last90.xlsx
+++ b/exports/sol-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>183.07</v>
+        <v>200.65</v>
       </c>
       <c r="C2" t="n">
-        <v>187.82</v>
+        <v>184.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.75</v>
+        <v>-16.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176.11</v>
+        <v>203.94</v>
       </c>
       <c r="C3" t="n">
-        <v>180.33</v>
+        <v>200.02</v>
       </c>
       <c r="D3" t="n">
-        <v>4.22</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>187.59</v>
+        <v>205.85</v>
       </c>
       <c r="C4" t="n">
-        <v>179.39</v>
+        <v>204.26</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>180.28</v>
+        <v>187.28</v>
       </c>
       <c r="C5" t="n">
-        <v>185.26</v>
+        <v>201.11</v>
       </c>
       <c r="D5" t="n">
-        <v>4.98</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200.65</v>
+        <v>195.91</v>
       </c>
       <c r="C6" t="n">
-        <v>184.46</v>
+        <v>190.24</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.19</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>203.94</v>
+        <v>202.92</v>
       </c>
       <c r="C7" t="n">
-        <v>200.07</v>
+        <v>197.36</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.86</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>205.85</v>
+        <v>214.41</v>
       </c>
       <c r="C8" t="n">
-        <v>204.24</v>
+        <v>204.21</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.61</v>
+        <v>-10.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187.28</v>
+        <v>205.22</v>
       </c>
       <c r="C9" t="n">
-        <v>201.12</v>
+        <v>210.61</v>
       </c>
       <c r="D9" t="n">
-        <v>13.84</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>195.91</v>
+        <v>202.86</v>
       </c>
       <c r="C10" t="n">
-        <v>190.21</v>
+        <v>205.44</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.69</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>202.92</v>
+        <v>200.86</v>
       </c>
       <c r="C11" t="n">
-        <v>197.4</v>
+        <v>203.93</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.52</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>214.41</v>
+        <v>197.11</v>
       </c>
       <c r="C12" t="n">
-        <v>204.22</v>
+        <v>200.15</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.19</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>205.22</v>
+        <v>209.48</v>
       </c>
       <c r="C13" t="n">
-        <v>210.63</v>
+        <v>199.33</v>
       </c>
       <c r="D13" t="n">
-        <v>5.41</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>202.86</v>
+        <v>210.75</v>
       </c>
       <c r="C14" t="n">
-        <v>205.42</v>
+        <v>208.64</v>
       </c>
       <c r="D14" t="n">
-        <v>2.56</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>200.86</v>
+        <v>202.56</v>
       </c>
       <c r="C15" t="n">
-        <v>203.95</v>
+        <v>209.23</v>
       </c>
       <c r="D15" t="n">
-        <v>3.08</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>197.11</v>
+        <v>203.5</v>
       </c>
       <c r="C16" t="n">
-        <v>200.15</v>
+        <v>202.64</v>
       </c>
       <c r="D16" t="n">
-        <v>3.04</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>209.48</v>
+        <v>200.25</v>
       </c>
       <c r="C17" t="n">
-        <v>199.33</v>
+        <v>203.28</v>
       </c>
       <c r="D17" t="n">
-        <v>-10.15</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>210.75</v>
+        <v>206.47</v>
       </c>
       <c r="C18" t="n">
-        <v>208.67</v>
+        <v>201.67</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.08</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>202.56</v>
+        <v>214.19</v>
       </c>
       <c r="C19" t="n">
-        <v>209.22</v>
+        <v>206.23</v>
       </c>
       <c r="D19" t="n">
-        <v>6.66</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>203.5</v>
+        <v>217.25</v>
       </c>
       <c r="C20" t="n">
-        <v>202.63</v>
+        <v>213.96</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.87</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>200.25</v>
+        <v>223.99</v>
       </c>
       <c r="C21" t="n">
-        <v>203.31</v>
+        <v>218.3</v>
       </c>
       <c r="D21" t="n">
-        <v>3.06</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>206.47</v>
+        <v>228.76</v>
       </c>
       <c r="C22" t="n">
-        <v>201.67</v>
+        <v>223.69</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>214.19</v>
+        <v>242.3</v>
       </c>
       <c r="C23" t="n">
-        <v>206.24</v>
+        <v>230.02</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.94</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>217.25</v>
+        <v>242.6</v>
       </c>
       <c r="C24" t="n">
-        <v>213.97</v>
+        <v>240.6</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.28</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>223.99</v>
+        <v>240.56</v>
       </c>
       <c r="C25" t="n">
-        <v>218.31</v>
+        <v>240.99</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.68</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>228.76</v>
+        <v>234.36</v>
       </c>
       <c r="C26" t="n">
-        <v>223.7</v>
+        <v>238.53</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.05</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>242.3</v>
+        <v>236.99</v>
       </c>
       <c r="C27" t="n">
-        <v>230.02</v>
+        <v>234.74</v>
       </c>
       <c r="D27" t="n">
-        <v>-12.28</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>242.6</v>
+        <v>244.86</v>
       </c>
       <c r="C28" t="n">
-        <v>240.63</v>
+        <v>237.79</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.96</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>240.56</v>
+        <v>247.64</v>
       </c>
       <c r="C29" t="n">
-        <v>240.99</v>
+        <v>244.44</v>
       </c>
       <c r="D29" t="n">
-        <v>0.43</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>234.36</v>
+        <v>238.55</v>
       </c>
       <c r="C30" t="n">
-        <v>238.54</v>
+        <v>245.16</v>
       </c>
       <c r="D30" t="n">
-        <v>4.18</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>236.99</v>
+        <v>239.59</v>
       </c>
       <c r="C31" t="n">
-        <v>234.75</v>
+        <v>239.43</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.24</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>244.86</v>
+        <v>236.58</v>
       </c>
       <c r="C32" t="n">
-        <v>237.81</v>
+        <v>238.97</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.05</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>247.64</v>
+        <v>220.5</v>
       </c>
       <c r="C33" t="n">
-        <v>244.46</v>
+        <v>232.08</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.17</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>238.55</v>
+        <v>213.72</v>
       </c>
       <c r="C34" t="n">
-        <v>245.16</v>
+        <v>218.75</v>
       </c>
       <c r="D34" t="n">
-        <v>6.61</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>239.59</v>
+        <v>211.76</v>
       </c>
       <c r="C35" t="n">
-        <v>239.43</v>
+        <v>213.77</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.16</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>236.58</v>
+        <v>192.38</v>
       </c>
       <c r="C36" t="n">
-        <v>238.99</v>
+        <v>207.2</v>
       </c>
       <c r="D36" t="n">
-        <v>2.41</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>220.5</v>
+        <v>205.35</v>
       </c>
       <c r="C37" t="n">
-        <v>232.07</v>
+        <v>195.9</v>
       </c>
       <c r="D37" t="n">
-        <v>11.57</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>213.72</v>
+        <v>203.58</v>
       </c>
       <c r="C38" t="n">
-        <v>218.74</v>
+        <v>204.78</v>
       </c>
       <c r="D38" t="n">
-        <v>5.03</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>211.76</v>
+        <v>210.74</v>
       </c>
       <c r="C39" t="n">
-        <v>213.78</v>
+        <v>206.29</v>
       </c>
       <c r="D39" t="n">
-        <v>2.03</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>192.38</v>
+        <v>213.05</v>
       </c>
       <c r="C40" t="n">
-        <v>207.21</v>
+        <v>210.54</v>
       </c>
       <c r="D40" t="n">
-        <v>14.83</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>205.35</v>
+        <v>208.74</v>
       </c>
       <c r="C41" t="n">
-        <v>195.87</v>
+        <v>212.8</v>
       </c>
       <c r="D41" t="n">
-        <v>-9.49</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>203.58</v>
+        <v>221.68</v>
       </c>
       <c r="C42" t="n">
-        <v>204.83</v>
+        <v>212.42</v>
       </c>
       <c r="D42" t="n">
-        <v>1.25</v>
+        <v>-9.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>210.74</v>
+        <v>234.86</v>
       </c>
       <c r="C43" t="n">
-        <v>206.27</v>
+        <v>222.64</v>
       </c>
       <c r="D43" t="n">
-        <v>-4.46</v>
+        <v>-12.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>213.05</v>
+        <v>233</v>
       </c>
       <c r="C44" t="n">
-        <v>210.56</v>
+        <v>233.07</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.5</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>208.74</v>
+        <v>228</v>
       </c>
       <c r="C45" t="n">
-        <v>212.8</v>
+        <v>231.12</v>
       </c>
       <c r="D45" t="n">
-        <v>4.06</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>221.68</v>
+        <v>228.6</v>
       </c>
       <c r="C46" t="n">
-        <v>212.41</v>
+        <v>227.85</v>
       </c>
       <c r="D46" t="n">
-        <v>-9.26</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>234.86</v>
+        <v>232.52</v>
       </c>
       <c r="C47" t="n">
-        <v>222.68</v>
+        <v>229.63</v>
       </c>
       <c r="D47" t="n">
-        <v>-12.18</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>233</v>
+        <v>220.48</v>
       </c>
       <c r="C48" t="n">
-        <v>233.09</v>
+        <v>228.82</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>228</v>
+        <v>229.1</v>
       </c>
       <c r="C49" t="n">
-        <v>231.12</v>
+        <v>221.58</v>
       </c>
       <c r="D49" t="n">
-        <v>3.12</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>228.6</v>
+        <v>220.99</v>
       </c>
       <c r="C50" t="n">
-        <v>227.85</v>
+        <v>226.72</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.75</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>232.52</v>
+        <v>188.66</v>
       </c>
       <c r="C51" t="n">
-        <v>229.65</v>
+        <v>212.98</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.87</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>220.48</v>
+        <v>178.05</v>
       </c>
       <c r="C52" t="n">
-        <v>228.84</v>
+        <v>185.31</v>
       </c>
       <c r="D52" t="n">
-        <v>8.359999999999999</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>229.1</v>
+        <v>197.51</v>
       </c>
       <c r="C53" t="n">
-        <v>221.57</v>
+        <v>183.16</v>
       </c>
       <c r="D53" t="n">
-        <v>-7.54</v>
+        <v>-14.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>220.99</v>
+        <v>208.37</v>
       </c>
       <c r="C54" t="n">
-        <v>226.76</v>
+        <v>199.4</v>
       </c>
       <c r="D54" t="n">
-        <v>5.77</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>188.66</v>
+        <v>202.46</v>
       </c>
       <c r="C55" t="n">
-        <v>212.97</v>
+        <v>204.7</v>
       </c>
       <c r="D55" t="n">
-        <v>24.3</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>178.05</v>
+        <v>194.02</v>
       </c>
       <c r="C56" t="n">
-        <v>185.28</v>
+        <v>200.51</v>
       </c>
       <c r="D56" t="n">
-        <v>7.23</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>197.51</v>
+        <v>184.69</v>
       </c>
       <c r="C57" t="n">
-        <v>183.19</v>
+        <v>194.17</v>
       </c>
       <c r="D57" t="n">
-        <v>-14.32</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>208.37</v>
+        <v>182.03</v>
       </c>
       <c r="C58" t="n">
-        <v>199.45</v>
+        <v>184.61</v>
       </c>
       <c r="D58" t="n">
-        <v>-8.92</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>202.46</v>
+        <v>187.66</v>
       </c>
       <c r="C59" t="n">
-        <v>204.71</v>
+        <v>181.92</v>
       </c>
       <c r="D59" t="n">
-        <v>2.25</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>194.02</v>
+        <v>187.8</v>
       </c>
       <c r="C60" t="n">
-        <v>200.51</v>
+        <v>185.65</v>
       </c>
       <c r="D60" t="n">
-        <v>6.49</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>184.69</v>
+        <v>189.75</v>
       </c>
       <c r="C61" t="n">
-        <v>194.17</v>
+        <v>186.9</v>
       </c>
       <c r="D61" t="n">
-        <v>9.48</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>182.03</v>
+        <v>185.67</v>
       </c>
       <c r="C62" t="n">
-        <v>184.61</v>
+        <v>187.78</v>
       </c>
       <c r="D62" t="n">
-        <v>2.58</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>187.66</v>
+        <v>180.15</v>
       </c>
       <c r="C63" t="n">
-        <v>181.95</v>
+        <v>184.4</v>
       </c>
       <c r="D63" t="n">
-        <v>-5.71</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>187.8</v>
+        <v>191.39</v>
       </c>
       <c r="C64" t="n">
-        <v>185.67</v>
+        <v>182.67</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.13</v>
+        <v>-8.710000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>189.75</v>
+        <v>193.56</v>
       </c>
       <c r="C65" t="n">
-        <v>186.9</v>
+        <v>190.55</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.85</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>185.67</v>
+        <v>194.04</v>
       </c>
       <c r="C66" t="n">
-        <v>187.8</v>
+        <v>193.11</v>
       </c>
       <c r="D66" t="n">
-        <v>2.13</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>180.15</v>
+        <v>200.03</v>
       </c>
       <c r="C67" t="n">
-        <v>184.41</v>
+        <v>193.93</v>
       </c>
       <c r="D67" t="n">
-        <v>4.26</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>191.39</v>
+        <v>198.74</v>
       </c>
       <c r="C68" t="n">
-        <v>182.68</v>
+        <v>199.27</v>
       </c>
       <c r="D68" t="n">
-        <v>-8.710000000000001</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>193.56</v>
+        <v>194.44</v>
       </c>
       <c r="C69" t="n">
-        <v>190.59</v>
+        <v>197.11</v>
       </c>
       <c r="D69" t="n">
-        <v>-2.97</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>194.04</v>
+        <v>194.41</v>
       </c>
       <c r="C70" t="n">
-        <v>193.12</v>
+        <v>193.18</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.92</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>200.03</v>
+        <v>184.62</v>
       </c>
       <c r="C71" t="n">
-        <v>193.93</v>
+        <v>191.26</v>
       </c>
       <c r="D71" t="n">
-        <v>-6.1</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>198.74</v>
+        <v>187.21</v>
       </c>
       <c r="C72" t="n">
-        <v>199.29</v>
+        <v>184.57</v>
       </c>
       <c r="D72" t="n">
-        <v>0.55</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>194.44</v>
+        <v>186.38</v>
       </c>
       <c r="C73" t="n">
-        <v>197.11</v>
+        <v>185.48</v>
       </c>
       <c r="D73" t="n">
-        <v>2.67</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>194.41</v>
+        <v>187.83</v>
       </c>
       <c r="C74" t="n">
-        <v>193.19</v>
+        <v>185.62</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.23</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>184.62</v>
+        <v>166.09</v>
       </c>
       <c r="C75" t="n">
-        <v>191.28</v>
+        <v>180.02</v>
       </c>
       <c r="D75" t="n">
-        <v>6.66</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>187.21</v>
+        <v>155.4</v>
       </c>
       <c r="C76" t="n">
-        <v>184.56</v>
+        <v>162.29</v>
       </c>
       <c r="D76" t="n">
-        <v>-2.65</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>186.38</v>
+        <v>162.57</v>
       </c>
       <c r="C77" t="n">
-        <v>185.51</v>
+        <v>157.46</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.87</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>187.83</v>
+        <v>155.07</v>
       </c>
       <c r="C78" t="n">
-        <v>185.62</v>
+        <v>159.51</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.2</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>166.09</v>
+        <v>161.71</v>
       </c>
       <c r="C79" t="n">
-        <v>180.03</v>
+        <v>155.38</v>
       </c>
       <c r="D79" t="n">
-        <v>13.94</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>155.4</v>
+        <v>158.1</v>
       </c>
       <c r="C80" t="n">
-        <v>162.26</v>
+        <v>159.55</v>
       </c>
       <c r="D80" t="n">
-        <v>6.86</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>162.57</v>
+        <v>164.45</v>
       </c>
       <c r="C81" t="n">
-        <v>157.48</v>
+        <v>161.79</v>
       </c>
       <c r="D81" t="n">
-        <v>-5.09</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>155.07</v>
+        <v>167.37</v>
       </c>
       <c r="C82" t="n">
-        <v>159.55</v>
+        <v>165.33</v>
       </c>
       <c r="D82" t="n">
-        <v>4.49</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>161.71</v>
+        <v>154.57</v>
       </c>
       <c r="C83" t="n">
-        <v>155.36</v>
+        <v>163.07</v>
       </c>
       <c r="D83" t="n">
-        <v>-6.35</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>158.1</v>
+        <v>153.26</v>
       </c>
       <c r="C84" t="n">
-        <v>159.59</v>
+        <v>154.03</v>
       </c>
       <c r="D84" t="n">
-        <v>1.49</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>164.45</v>
+        <v>145.11</v>
       </c>
       <c r="C85" t="n">
-        <v>161.78</v>
+        <v>150.31</v>
       </c>
       <c r="D85" t="n">
-        <v>-2.67</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>167.37</v>
+        <v>138.68</v>
       </c>
       <c r="C86" t="n">
-        <v>165.35</v>
+        <v>142.96</v>
       </c>
       <c r="D86" t="n">
-        <v>-2.02</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>154.57</v>
+        <v>139.54</v>
       </c>
       <c r="C87" t="n">
-        <v>163.08</v>
+        <v>138.25</v>
       </c>
       <c r="D87" t="n">
-        <v>8.51</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>153.26</v>
+        <v>137.27</v>
       </c>
       <c r="C88" t="n">
-        <v>154.01</v>
+        <v>138.03</v>
       </c>
       <c r="D88" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>145.11</v>
+        <v>130.85</v>
       </c>
       <c r="C89" t="n">
-        <v>150.33</v>
+        <v>134.45</v>
       </c>
       <c r="D89" t="n">
-        <v>5.23</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>138.68</v>
+        <v>140.71</v>
       </c>
       <c r="C90" t="n">
-        <v>142.96</v>
+        <v>133.98</v>
       </c>
       <c r="D90" t="n">
-        <v>4.28</v>
+        <v>-6.74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>139.54</v>
+        <v>136.77</v>
       </c>
       <c r="C91" t="n">
-        <v>138.27</v>
+        <v>139.34</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.27</v>
+        <v>2.57</v>
       </c>
     </row>
   </sheetData>

--- a/exports/sol-usd_predictions_last90.xlsx
+++ b/exports/sol-usd_predictions_last90.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,1446 +449,2669 @@
           <t>diff</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>diff_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_start_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>train_end_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200.65</v>
+        <v>205.85</v>
       </c>
       <c r="C2" t="n">
-        <v>184.5</v>
+        <v>200.19</v>
       </c>
       <c r="D2" t="n">
-        <v>-16.15</v>
+        <v>-5.66</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203.94</v>
+        <v>187.28</v>
       </c>
       <c r="C3" t="n">
-        <v>200.02</v>
+        <v>205.12</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.92</v>
+        <v>17.84</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>205.85</v>
+        <v>195.91</v>
       </c>
       <c r="C4" t="n">
-        <v>204.26</v>
+        <v>201.52</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.59</v>
+        <v>5.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>187.28</v>
+        <v>202.92</v>
       </c>
       <c r="C5" t="n">
-        <v>201.11</v>
+        <v>189.55</v>
       </c>
       <c r="D5" t="n">
-        <v>13.83</v>
+        <v>-13.37</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>195.91</v>
+        <v>214.41</v>
       </c>
       <c r="C6" t="n">
-        <v>190.24</v>
+        <v>197.06</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.67</v>
+        <v>-17.34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202.92</v>
+        <v>205.22</v>
       </c>
       <c r="C7" t="n">
-        <v>197.36</v>
+        <v>204.21</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.56</v>
+        <v>-1.01</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>214.41</v>
+        <v>202.86</v>
       </c>
       <c r="C8" t="n">
-        <v>204.21</v>
+        <v>211.34</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.19</v>
+        <v>8.48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>205.22</v>
+        <v>200.86</v>
       </c>
       <c r="C9" t="n">
-        <v>210.61</v>
+        <v>205.55</v>
       </c>
       <c r="D9" t="n">
-        <v>5.39</v>
+        <v>4.69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202.86</v>
+        <v>197.11</v>
       </c>
       <c r="C10" t="n">
-        <v>205.44</v>
+        <v>203.85</v>
       </c>
       <c r="D10" t="n">
-        <v>2.58</v>
+        <v>6.74</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>200.86</v>
+        <v>209.48</v>
       </c>
       <c r="C11" t="n">
-        <v>203.93</v>
+        <v>200.13</v>
       </c>
       <c r="D11" t="n">
-        <v>3.07</v>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>197.11</v>
+        <v>210.75</v>
       </c>
       <c r="C12" t="n">
-        <v>200.15</v>
+        <v>199.27</v>
       </c>
       <c r="D12" t="n">
-        <v>3.04</v>
+        <v>-11.48</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>209.48</v>
+        <v>202.56</v>
       </c>
       <c r="C13" t="n">
-        <v>199.33</v>
+        <v>208.81</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.15</v>
+        <v>6.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>210.75</v>
+        <v>203.5</v>
       </c>
       <c r="C14" t="n">
-        <v>208.64</v>
+        <v>209.65</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.11</v>
+        <v>6.15</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>202.56</v>
+        <v>200.25</v>
       </c>
       <c r="C15" t="n">
-        <v>209.23</v>
+        <v>202.86</v>
       </c>
       <c r="D15" t="n">
-        <v>6.67</v>
+        <v>2.62</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>203.5</v>
+        <v>206.47</v>
       </c>
       <c r="C16" t="n">
-        <v>202.64</v>
+        <v>203.11</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.86</v>
+        <v>-3.36</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>200.25</v>
+        <v>214.19</v>
       </c>
       <c r="C17" t="n">
-        <v>203.28</v>
+        <v>201.75</v>
       </c>
       <c r="D17" t="n">
-        <v>3.04</v>
+        <v>-12.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>206.47</v>
+        <v>217.25</v>
       </c>
       <c r="C18" t="n">
-        <v>201.67</v>
+        <v>206.71</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.8</v>
+        <v>-10.54</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>214.19</v>
+        <v>223.99</v>
       </c>
       <c r="C19" t="n">
-        <v>206.23</v>
+        <v>214.24</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.95</v>
+        <v>-9.75</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>217.25</v>
+        <v>228.76</v>
       </c>
       <c r="C20" t="n">
-        <v>213.96</v>
+        <v>218.58</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.29</v>
+        <v>-10.18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>223.99</v>
+        <v>242.3</v>
       </c>
       <c r="C21" t="n">
-        <v>218.3</v>
+        <v>223.92</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.68</v>
+        <v>-18.38</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-7.59</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>228.76</v>
+        <v>242.6</v>
       </c>
       <c r="C22" t="n">
-        <v>223.69</v>
+        <v>230.36</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.07</v>
+        <v>-12.23</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>242.3</v>
+        <v>240.56</v>
       </c>
       <c r="C23" t="n">
-        <v>230.02</v>
+        <v>240.95</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.28</v>
+        <v>0.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>242.6</v>
+        <v>234.36</v>
       </c>
       <c r="C24" t="n">
-        <v>240.6</v>
+        <v>241.54</v>
       </c>
       <c r="D24" t="n">
-        <v>-2</v>
+        <v>7.18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>240.56</v>
+        <v>236.99</v>
       </c>
       <c r="C25" t="n">
-        <v>240.99</v>
+        <v>238.83</v>
       </c>
       <c r="D25" t="n">
-        <v>0.43</v>
+        <v>1.84</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>234.36</v>
+        <v>244.86</v>
       </c>
       <c r="C26" t="n">
-        <v>238.53</v>
+        <v>234.71</v>
       </c>
       <c r="D26" t="n">
-        <v>4.17</v>
+        <v>-10.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>236.99</v>
+        <v>247.64</v>
       </c>
       <c r="C27" t="n">
-        <v>234.74</v>
+        <v>238.07</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.25</v>
+        <v>-9.57</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="C28" t="n">
         <v>244.86</v>
       </c>
-      <c r="C28" t="n">
-        <v>237.79</v>
-      </c>
       <c r="D28" t="n">
-        <v>-7.06</v>
+        <v>6.3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>247.64</v>
+        <v>239.59</v>
       </c>
       <c r="C29" t="n">
-        <v>244.44</v>
+        <v>245.75</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.2</v>
+        <v>6.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>238.55</v>
+        <v>236.58</v>
       </c>
       <c r="C30" t="n">
-        <v>245.16</v>
+        <v>239.53</v>
       </c>
       <c r="D30" t="n">
-        <v>6.61</v>
+        <v>2.95</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>239.59</v>
+        <v>220.5</v>
       </c>
       <c r="C31" t="n">
-        <v>239.43</v>
+        <v>239.25</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.16</v>
+        <v>18.76</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>236.58</v>
+        <v>213.72</v>
       </c>
       <c r="C32" t="n">
-        <v>238.97</v>
+        <v>233.27</v>
       </c>
       <c r="D32" t="n">
-        <v>2.39</v>
+        <v>19.55</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>220.5</v>
+        <v>211.76</v>
       </c>
       <c r="C33" t="n">
-        <v>232.08</v>
+        <v>218.78</v>
       </c>
       <c r="D33" t="n">
-        <v>11.59</v>
+        <v>7.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>213.72</v>
+        <v>192.38</v>
       </c>
       <c r="C34" t="n">
-        <v>218.75</v>
+        <v>213.76</v>
       </c>
       <c r="D34" t="n">
-        <v>5.04</v>
+        <v>21.38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>211.76</v>
+        <v>205.35</v>
       </c>
       <c r="C35" t="n">
-        <v>213.77</v>
+        <v>207.52</v>
       </c>
       <c r="D35" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>192.38</v>
+        <v>203.58</v>
       </c>
       <c r="C36" t="n">
-        <v>207.2</v>
+        <v>195.53</v>
       </c>
       <c r="D36" t="n">
-        <v>14.82</v>
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>205.35</v>
+        <v>210.74</v>
       </c>
       <c r="C37" t="n">
-        <v>195.9</v>
+        <v>204.73</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>203.58</v>
+        <v>213.05</v>
       </c>
       <c r="C38" t="n">
-        <v>204.78</v>
+        <v>206.69</v>
       </c>
       <c r="D38" t="n">
-        <v>1.19</v>
+        <v>-6.36</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>210.74</v>
+        <v>208.74</v>
       </c>
       <c r="C39" t="n">
-        <v>206.29</v>
+        <v>211</v>
       </c>
       <c r="D39" t="n">
-        <v>-4.44</v>
+        <v>2.26</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>213.05</v>
+        <v>221.68</v>
       </c>
       <c r="C40" t="n">
-        <v>210.54</v>
+        <v>213.17</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.52</v>
+        <v>-8.51</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>208.74</v>
+        <v>234.86</v>
       </c>
       <c r="C41" t="n">
-        <v>212.8</v>
+        <v>212.47</v>
       </c>
       <c r="D41" t="n">
-        <v>4.05</v>
+        <v>-22.38</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>221.68</v>
+        <v>233</v>
       </c>
       <c r="C42" t="n">
-        <v>212.42</v>
+        <v>222.77</v>
       </c>
       <c r="D42" t="n">
-        <v>-9.26</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>234.86</v>
+        <v>228</v>
       </c>
       <c r="C43" t="n">
-        <v>222.64</v>
+        <v>233.82</v>
       </c>
       <c r="D43" t="n">
-        <v>-12.21</v>
+        <v>5.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>233</v>
+        <v>228.6</v>
       </c>
       <c r="C44" t="n">
-        <v>233.07</v>
+        <v>231.48</v>
       </c>
       <c r="D44" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.87</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>232.52</v>
+      </c>
+      <c r="C45" t="n">
         <v>228</v>
       </c>
-      <c r="C45" t="n">
-        <v>231.12</v>
-      </c>
       <c r="D45" t="n">
-        <v>3.11</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>228.6</v>
+        <v>220.48</v>
       </c>
       <c r="C46" t="n">
-        <v>227.85</v>
+        <v>229.63</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.75</v>
+        <v>9.15</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>232.52</v>
+        <v>229.1</v>
       </c>
       <c r="C47" t="n">
-        <v>229.63</v>
+        <v>229.16</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.88</v>
+        <v>0.05</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>220.48</v>
+        <v>220.99</v>
       </c>
       <c r="C48" t="n">
-        <v>228.82</v>
+        <v>221.63</v>
       </c>
       <c r="D48" t="n">
-        <v>8.34</v>
+        <v>0.64</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>229.1</v>
+        <v>188.66</v>
       </c>
       <c r="C49" t="n">
-        <v>221.58</v>
+        <v>227</v>
       </c>
       <c r="D49" t="n">
-        <v>-7.52</v>
+        <v>38.34</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20.32</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>220.99</v>
+        <v>178.05</v>
       </c>
       <c r="C50" t="n">
-        <v>226.72</v>
+        <v>213.91</v>
       </c>
       <c r="D50" t="n">
-        <v>5.73</v>
+        <v>35.85</v>
+      </c>
+      <c r="E50" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>188.66</v>
+        <v>197.51</v>
       </c>
       <c r="C51" t="n">
-        <v>212.98</v>
+        <v>184.93</v>
       </c>
       <c r="D51" t="n">
-        <v>24.31</v>
+        <v>-12.58</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>178.05</v>
+        <v>208.37</v>
       </c>
       <c r="C52" t="n">
-        <v>185.31</v>
+        <v>182.52</v>
       </c>
       <c r="D52" t="n">
-        <v>7.25</v>
+        <v>-25.85</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>197.51</v>
+        <v>202.46</v>
       </c>
       <c r="C53" t="n">
-        <v>183.16</v>
+        <v>199.7</v>
       </c>
       <c r="D53" t="n">
-        <v>-14.34</v>
+        <v>-2.76</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>208.37</v>
+        <v>194.02</v>
       </c>
       <c r="C54" t="n">
-        <v>199.4</v>
+        <v>205.37</v>
       </c>
       <c r="D54" t="n">
-        <v>-8.970000000000001</v>
+        <v>11.34</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>202.46</v>
+        <v>184.69</v>
       </c>
       <c r="C55" t="n">
-        <v>204.7</v>
+        <v>200.92</v>
       </c>
       <c r="D55" t="n">
-        <v>2.24</v>
+        <v>16.23</v>
+      </c>
+      <c r="E55" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>194.02</v>
+        <v>182.03</v>
       </c>
       <c r="C56" t="n">
-        <v>200.51</v>
+        <v>194.39</v>
       </c>
       <c r="D56" t="n">
-        <v>6.49</v>
+        <v>12.35</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>184.69</v>
+        <v>187.66</v>
       </c>
       <c r="C57" t="n">
-        <v>194.17</v>
+        <v>184.8</v>
       </c>
       <c r="D57" t="n">
-        <v>9.48</v>
+        <v>-2.86</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>182.03</v>
+        <v>187.8</v>
       </c>
       <c r="C58" t="n">
-        <v>184.61</v>
+        <v>182.1</v>
       </c>
       <c r="D58" t="n">
-        <v>2.57</v>
+        <v>-5.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>187.66</v>
+        <v>189.75</v>
       </c>
       <c r="C59" t="n">
-        <v>181.92</v>
+        <v>185.9</v>
       </c>
       <c r="D59" t="n">
-        <v>-5.74</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>187.8</v>
+        <v>185.67</v>
       </c>
       <c r="C60" t="n">
-        <v>185.65</v>
+        <v>187.12</v>
       </c>
       <c r="D60" t="n">
-        <v>-2.15</v>
+        <v>1.45</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>189.75</v>
+        <v>180.15</v>
       </c>
       <c r="C61" t="n">
-        <v>186.9</v>
+        <v>188.06</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.85</v>
+        <v>7.91</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>185.67</v>
+        <v>191.39</v>
       </c>
       <c r="C62" t="n">
-        <v>187.78</v>
+        <v>184.53</v>
       </c>
       <c r="D62" t="n">
-        <v>2.11</v>
+        <v>-6.86</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>180.15</v>
+        <v>193.56</v>
       </c>
       <c r="C63" t="n">
-        <v>184.4</v>
+        <v>182.81</v>
       </c>
       <c r="D63" t="n">
-        <v>4.25</v>
+        <v>-10.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>191.39</v>
+        <v>194.04</v>
       </c>
       <c r="C64" t="n">
-        <v>182.67</v>
+        <v>190.79</v>
       </c>
       <c r="D64" t="n">
-        <v>-8.710000000000001</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>193.56</v>
+        <v>200.03</v>
       </c>
       <c r="C65" t="n">
-        <v>190.55</v>
+        <v>193.13</v>
       </c>
       <c r="D65" t="n">
-        <v>-3.01</v>
+        <v>-6.9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>194.04</v>
+        <v>198.74</v>
       </c>
       <c r="C66" t="n">
-        <v>193.11</v>
+        <v>194.18</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.93</v>
+        <v>-4.57</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>200.03</v>
+        <v>194.44</v>
       </c>
       <c r="C67" t="n">
-        <v>193.93</v>
+        <v>199.53</v>
       </c>
       <c r="D67" t="n">
-        <v>-6.1</v>
+        <v>5.09</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>198.74</v>
+        <v>194.41</v>
       </c>
       <c r="C68" t="n">
-        <v>199.27</v>
+        <v>197.36</v>
       </c>
       <c r="D68" t="n">
-        <v>0.53</v>
+        <v>2.95</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>194.44</v>
+        <v>184.62</v>
       </c>
       <c r="C69" t="n">
-        <v>197.11</v>
+        <v>193.46</v>
       </c>
       <c r="D69" t="n">
-        <v>2.67</v>
+        <v>8.83</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>194.41</v>
+        <v>187.21</v>
       </c>
       <c r="C70" t="n">
-        <v>193.18</v>
+        <v>191.5</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.23</v>
+        <v>4.29</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>184.62</v>
+        <v>186.38</v>
       </c>
       <c r="C71" t="n">
-        <v>191.26</v>
+        <v>184.72</v>
       </c>
       <c r="D71" t="n">
-        <v>6.63</v>
+        <v>-1.66</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>187.21</v>
+        <v>187.83</v>
       </c>
       <c r="C72" t="n">
-        <v>184.57</v>
+        <v>185.72</v>
       </c>
       <c r="D72" t="n">
-        <v>-2.64</v>
+        <v>-2.11</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>186.38</v>
+        <v>166.09</v>
       </c>
       <c r="C73" t="n">
-        <v>185.48</v>
+        <v>185.86</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9</v>
+        <v>19.77</v>
+      </c>
+      <c r="E73" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>187.83</v>
+        <v>155.4</v>
       </c>
       <c r="C74" t="n">
-        <v>185.62</v>
+        <v>180.48</v>
       </c>
       <c r="D74" t="n">
-        <v>-2.21</v>
+        <v>25.07</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>166.09</v>
+        <v>162.57</v>
       </c>
       <c r="C75" t="n">
-        <v>180.02</v>
+        <v>162.36</v>
       </c>
       <c r="D75" t="n">
-        <v>13.93</v>
+        <v>-0.2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>155.4</v>
+        <v>155.07</v>
       </c>
       <c r="C76" t="n">
-        <v>162.29</v>
+        <v>157.62</v>
       </c>
       <c r="D76" t="n">
-        <v>6.88</v>
+        <v>2.55</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>162.57</v>
+        <v>161.71</v>
       </c>
       <c r="C77" t="n">
-        <v>157.46</v>
+        <v>159.59</v>
       </c>
       <c r="D77" t="n">
-        <v>-5.11</v>
+        <v>-2.12</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>155.07</v>
+        <v>158.1</v>
       </c>
       <c r="C78" t="n">
-        <v>159.51</v>
+        <v>155.37</v>
       </c>
       <c r="D78" t="n">
-        <v>4.44</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>161.71</v>
+        <v>164.45</v>
       </c>
       <c r="C79" t="n">
-        <v>155.38</v>
+        <v>159.62</v>
       </c>
       <c r="D79" t="n">
-        <v>-6.33</v>
+        <v>-4.83</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>158.1</v>
+        <v>167.37</v>
       </c>
       <c r="C80" t="n">
-        <v>159.55</v>
+        <v>161.75</v>
       </c>
       <c r="D80" t="n">
-        <v>1.45</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>164.45</v>
+        <v>154.57</v>
       </c>
       <c r="C81" t="n">
-        <v>161.79</v>
+        <v>165.43</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.66</v>
+        <v>10.86</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>167.37</v>
+        <v>153.26</v>
       </c>
       <c r="C82" t="n">
-        <v>165.33</v>
+        <v>163.19</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.04</v>
+        <v>9.92</v>
+      </c>
+      <c r="E82" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>154.57</v>
+        <v>145.11</v>
       </c>
       <c r="C83" t="n">
-        <v>163.07</v>
+        <v>154.12</v>
       </c>
       <c r="D83" t="n">
-        <v>8.5</v>
+        <v>9.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>153.26</v>
+        <v>138.68</v>
       </c>
       <c r="C84" t="n">
-        <v>154.03</v>
+        <v>150.43</v>
       </c>
       <c r="D84" t="n">
-        <v>0.77</v>
+        <v>11.75</v>
+      </c>
+      <c r="E84" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>145.11</v>
+        <v>139.54</v>
       </c>
       <c r="C85" t="n">
-        <v>150.31</v>
+        <v>142.98</v>
       </c>
       <c r="D85" t="n">
-        <v>5.2</v>
+        <v>3.44</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>138.68</v>
+        <v>137.27</v>
       </c>
       <c r="C86" t="n">
-        <v>142.96</v>
+        <v>138.27</v>
       </c>
       <c r="D86" t="n">
-        <v>4.28</v>
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>139.54</v>
+        <v>130.85</v>
       </c>
       <c r="C87" t="n">
-        <v>138.25</v>
+        <v>138.04</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.28</v>
+        <v>7.2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>137.27</v>
+        <v>140.71</v>
       </c>
       <c r="C88" t="n">
-        <v>138.03</v>
+        <v>134.42</v>
       </c>
       <c r="D88" t="n">
-        <v>0.76</v>
+        <v>-6.3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>130.85</v>
+        <v>136.77</v>
       </c>
       <c r="C89" t="n">
-        <v>134.45</v>
+        <v>133.98</v>
       </c>
       <c r="D89" t="n">
-        <v>3.6</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>140.71</v>
+        <v>133.52</v>
       </c>
       <c r="C90" t="n">
-        <v>133.98</v>
+        <v>139.37</v>
       </c>
       <c r="D90" t="n">
-        <v>-6.74</v>
+        <v>5.86</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>136.77</v>
+        <v>128.5</v>
       </c>
       <c r="C91" t="n">
-        <v>139.34</v>
+        <v>135.54</v>
       </c>
       <c r="D91" t="n">
-        <v>2.57</v>
-      </c>
+        <v>7.04</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AVG_TRIM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>(ex max/min)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
